--- a/Coupang_Top20_20260613.xlsx
+++ b/Coupang_Top20_20260613.xlsx
@@ -462,28 +462,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Apple USB-C 커넥터 EarPods</t>
+          <t>아이리버 C타입-C타입 패브릭 초고속 충전 데이터 케이블 60W</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26990</v>
+        <v>5090</v>
       </c>
       <c r="C3">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8300107736&amp;itemId=25246423475&amp;vendorItemId=90965273088&amp;traceid=V0-113-6d3bd893a0f3e865", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8803472212&amp;itemId=25636725400&amp;vendorItemId=92626790654&amp;traceid=V0-113-4e0e1cdf04169745", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한경희생활과학 초미세풍 발터치 리모컨 선풍기</t>
+          <t>아이리버 25W 2포트 초고속 가정용 충전기 + CtoC 케이블 세트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39510</v>
+        <v>8800</v>
       </c>
       <c r="C4">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8049298764&amp;itemId=22568615219&amp;vendorItemId=89610481080&amp;traceid=V0-113-c6225c8b32161464", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8939019740&amp;itemId=26138373322&amp;vendorItemId=93118512226&amp;traceid=V0-113-fd1e07a2d9481cd8", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
@@ -532,14 +532,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홈플래닛 발터치 리모컨 스탠드형 선풍기</t>
+          <t>Apple 2024 에어팟 4 액티브 노이즈 캔슬링 블루투스 이어폰</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32890</v>
+        <v>241690</v>
       </c>
       <c r="C8">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=1459643219&amp;itemId=2511597502&amp;vendorItemId=92134731921&amp;traceid=V0-113-62386184a6cb7f37", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8367073894&amp;itemId=24175708331&amp;vendorItemId=91193685703&amp;traceid=V0-113-8955d242cb33fcee", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
@@ -560,28 +560,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필립스 무선 ENC노이즈캔슬링 블루투스 이어폰</t>
+          <t>PLEIGO USB 메모리 P50</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19900</v>
+        <v>9750</v>
       </c>
       <c r="C10">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8498887873&amp;itemId=24600675528&amp;vendorItemId=91612183770&amp;traceid=V0-113-53ee2dd24dc6f077", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=5309101612&amp;itemId=18278617989&amp;vendorItemId=74945175742&amp;traceid=V0-113-09bac7b5f3f4541f", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>로지텍 무소음 무선 마우스</t>
+          <t>필립스 무선 ENC노이즈캔슬링 블루투스 이어폰</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25200</v>
+        <v>19900</v>
       </c>
       <c r="C11">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6159950381&amp;itemId=11948008563&amp;vendorItemId=3299873959&amp;traceid=V0-113-a5be5e5f7b0a2d69", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8498887873&amp;itemId=24600675528&amp;vendorItemId=91612183770&amp;traceid=V0-113-53ee2dd24dc6f077", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
@@ -602,126 +602,126 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PLEIGO USB 메모리 P50</t>
+          <t>Apple 정품 라이트닝 이어팟</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9750</v>
+        <v>27160</v>
       </c>
       <c r="C13">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=5309101612&amp;itemId=18278617989&amp;vendorItemId=74945175742&amp;traceid=V0-113-09bac7b5f3f4541f", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=5001745972&amp;itemId=23686271502&amp;vendorItemId=90711442673&amp;traceid=V0-113-57599c7d00aef45d", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Apple 정품 20W USB-C 전원 어댑터 MUW13KH/A</t>
+          <t>루메나 무선 탁상용선풍기</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21050</v>
+        <v>35590</v>
       </c>
       <c r="C14">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=2270230024&amp;itemId=22170383583&amp;vendorItemId=88946948908&amp;traceid=V0-113-fad4b0f7464d90db", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9041217547&amp;itemId=22524207601&amp;vendorItemId=89545588602&amp;traceid=V0-113-93af8ab0ce6bd264", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>홈플래닛 퀄컴 공식인증 QC3.0 18W 고속충전기 + C타입 충전케이블 1.2m 세트</t>
+          <t>신지모루 C to C PD 고속충전 케이블 60W</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7490</v>
+        <v>6900</v>
       </c>
       <c r="C15">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=1628630781&amp;itemId=2778296479&amp;vendorItemId=89645323681&amp;traceid=V0-113-e16801aaf71b1d25", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=9344838202&amp;itemId=13761827932&amp;vendorItemId=81012487257&amp;traceid=V0-113-0a9564caf484529f", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>액센 프리미엄 캐릭터 마이크로 SD카드</t>
+          <t>유닉스 세라믹 판고데기</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19000</v>
+        <v>24900</v>
       </c>
       <c r="C16">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7704604385&amp;itemId=6156844140&amp;vendorItemId=73453040955&amp;traceid=V0-113-a6ffe7d8068452b2", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8729115745&amp;itemId=25361584612&amp;vendorItemId=3089081003&amp;traceid=V0-113-c054456fc302c5b1", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>홈플래닛 탁상용 접이식 스마트폰 거치대  6.5x11x12.5~16.5 cm</t>
+          <t>아이리버 3.5mm AUX 갤럭시 노트북 컴퓨터 알루미늄 커널형 유선 이어폰, BHC-70M, 블랙</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3290</v>
+        <v>7900</v>
       </c>
       <c r="C17">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7852115665&amp;itemId=21404472558&amp;vendorItemId=88461047256&amp;traceid=V0-113-d78df725617adad0", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8602654934&amp;itemId=24944896878&amp;vendorItemId=91980127301&amp;traceid=V0-113-cef1a24c3259468a", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>유닉스 세라믹 판고데기</t>
+          <t>에버튼하우스 에그쿠커</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24900</v>
+        <v>8500</v>
       </c>
       <c r="C18">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8729115745&amp;itemId=25361584612&amp;vendorItemId=3089081003&amp;traceid=V0-113-c054456fc302c5b1", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=283693738&amp;itemId=18656743421&amp;vendorItemId=70683242414&amp;traceid=V0-113-c77feddeeb9a1c86", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Apple 정품 라이트닝 이어팟</t>
+          <t>쿠쿠 전자레인지 다이얼식 20L</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27160</v>
+        <v>59290</v>
       </c>
       <c r="C19">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=5001745972&amp;itemId=23686271502&amp;vendorItemId=90711442673&amp;traceid=V0-113-57599c7d00aef45d", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=6784715012&amp;itemId=15967393537&amp;vendorItemId=5493101444&amp;traceid=V0-113-70e181a43b411328", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>신지모루 로프 C타입 고속충전 케이블</t>
+          <t>홈플래닛 디지털 LED 가정용 체중계</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8900</v>
+        <v>8990</v>
       </c>
       <c r="C20">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7900401137&amp;itemId=926533007&amp;vendorItemId=5302365610&amp;traceid=V0-113-c1147fc604802442", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8359676766&amp;itemId=24158126424&amp;vendorItemId=91176755808&amp;traceid=V0-113-bd08c10e4eabdcc5", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>아이리버 3.5mm AUX 갤럭시 노트북 컴퓨터 알루미늄 커널형 유선 이어폰, BHC-70M, 블랙</t>
+          <t>프라임큐 C타입 오픈형 유선 이어폰</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7900</v>
+        <v>5830</v>
       </c>
       <c r="C21">
-        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=8602654934&amp;itemId=24944896878&amp;vendorItemId=91980127301&amp;traceid=V0-113-cef1a24c3259468a", "클릭해서 이동")</f>
+        <f>HYPERLINK("https://link.coupang.com/re/AFFSDP?lptag=AF2411847&amp;pageKey=7842640108&amp;itemId=21353802010&amp;vendorItemId=81754468157&amp;traceid=V0-113-d555f442edff9f15", "클릭해서 이동")</f>
         <v/>
       </c>
     </row>
